--- a/backend/data/financials_by_company/0CM.F.xlsx
+++ b/backend/data/financials_by_company/0CM.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,129 +624,67 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Impairment Of Capital Assets</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-218419</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-15375</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-15375</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-233794</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-233794</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-233794</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="L2" t="n">
-        <v>233794</v>
-      </c>
-      <c r="M2" t="n">
-        <v>24000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>67873334</v>
-      </c>
-      <c r="O2" t="n">
-        <v>67873334</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-249169</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-15375</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>6856</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-6856</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-22231</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-233794</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>233794</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>81857</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>151937</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>7852</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>144085</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>42085</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>24000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>78000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>10753</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>-10753</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -755,103 +693,103 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-349890</v>
+        <v>-434161</v>
       </c>
       <c r="E3" t="n">
-        <v>35722</v>
+        <v>-33523</v>
       </c>
       <c r="F3" t="n">
-        <v>35722</v>
+        <v>-33523</v>
       </c>
       <c r="G3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="H3" t="n">
-        <v>-314168</v>
+        <v>-467684</v>
       </c>
       <c r="I3" t="n">
-        <v>-314168</v>
+        <v>-467684</v>
       </c>
       <c r="J3" t="n">
-        <v>-314168</v>
+        <v>-467684</v>
       </c>
       <c r="K3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="L3" t="n">
-        <v>314168</v>
+        <v>467684</v>
       </c>
       <c r="M3" t="n">
-        <v>24000</v>
+        <v>28223</v>
       </c>
       <c r="N3" t="n">
-        <v>67380183</v>
+        <v>65946551</v>
       </c>
       <c r="O3" t="n">
-        <v>67380183</v>
+        <v>65946551</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="S3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="T3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="U3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="V3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-278446</v>
+        <v>-501207</v>
       </c>
       <c r="Y3" t="n">
-        <v>35722</v>
+        <v>-33523</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>31707</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-31707</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>4015</v>
+        <v>-33523</v>
       </c>
       <c r="AD3" t="n">
-        <v>-314168</v>
+        <v>-467684</v>
       </c>
       <c r="AE3" t="n">
-        <v>314168</v>
+        <v>467684</v>
       </c>
       <c r="AF3" t="n">
-        <v>82267</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>96250</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>231901</v>
+        <v>371434</v>
       </c>
       <c r="AI3" t="n">
-        <v>6279</v>
+        <v>115492</v>
       </c>
       <c r="AJ3" t="n">
-        <v>225622</v>
+        <v>255942</v>
       </c>
       <c r="AK3" t="n">
-        <v>57622</v>
+        <v>83719</v>
       </c>
       <c r="AL3" t="n">
-        <v>24000</v>
+        <v>28223</v>
       </c>
       <c r="AM3" t="n">
         <v>144000</v>
@@ -862,10 +800,11 @@
       <c r="AO3" t="n">
         <v>0</v>
       </c>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -874,103 +813,103 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-434161</v>
+        <v>-349890</v>
       </c>
       <c r="E4" t="n">
-        <v>-33523</v>
+        <v>35722</v>
       </c>
       <c r="F4" t="n">
-        <v>-33523</v>
+        <v>35722</v>
       </c>
       <c r="G4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="H4" t="n">
-        <v>-467684</v>
+        <v>-314168</v>
       </c>
       <c r="I4" t="n">
-        <v>-467684</v>
+        <v>-314168</v>
       </c>
       <c r="J4" t="n">
-        <v>-467684</v>
+        <v>-314168</v>
       </c>
       <c r="K4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="L4" t="n">
-        <v>467684</v>
+        <v>314168</v>
       </c>
       <c r="M4" t="n">
-        <v>28223</v>
+        <v>24000</v>
       </c>
       <c r="N4" t="n">
-        <v>65946551</v>
+        <v>67380183</v>
       </c>
       <c r="O4" t="n">
-        <v>65946551</v>
+        <v>67380183</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="S4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="T4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="U4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="V4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-501207</v>
+        <v>-278446</v>
       </c>
       <c r="Y4" t="n">
-        <v>-33523</v>
+        <v>35722</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>31707</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-31707</v>
+      </c>
       <c r="AC4" t="n">
-        <v>-33523</v>
+        <v>4015</v>
       </c>
       <c r="AD4" t="n">
-        <v>-467684</v>
+        <v>-314168</v>
       </c>
       <c r="AE4" t="n">
-        <v>467684</v>
+        <v>314168</v>
       </c>
       <c r="AF4" t="n">
-        <v>96250</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>82267</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>371434</v>
+        <v>231901</v>
       </c>
       <c r="AI4" t="n">
-        <v>115492</v>
+        <v>6279</v>
       </c>
       <c r="AJ4" t="n">
-        <v>255942</v>
+        <v>225622</v>
       </c>
       <c r="AK4" t="n">
-        <v>83719</v>
+        <v>57622</v>
       </c>
       <c r="AL4" t="n">
-        <v>28223</v>
+        <v>24000</v>
       </c>
       <c r="AM4" t="n">
         <v>144000</v>
@@ -981,10 +920,11 @@
       <c r="AO4" t="n">
         <v>0</v>
       </c>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -993,108 +933,237 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-921602</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>-218419</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-15375</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-15375</v>
+      </c>
       <c r="G5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="H5" t="n">
-        <v>-921602</v>
+        <v>-233794</v>
       </c>
       <c r="I5" t="n">
-        <v>-921602</v>
+        <v>-233794</v>
       </c>
       <c r="J5" t="n">
-        <v>-921602</v>
+        <v>-233794</v>
       </c>
       <c r="K5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="L5" t="n">
-        <v>921602</v>
+        <v>233794</v>
       </c>
       <c r="M5" t="n">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="N5" t="n">
-        <v>55647351</v>
+        <v>67873334</v>
       </c>
       <c r="O5" t="n">
-        <v>55647351</v>
+        <v>67873334</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="S5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="T5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="U5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="V5" t="n">
-        <v>-921602</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
+        <v>-249169</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
       </c>
       <c r="Y5" t="n">
-        <v>10753</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10753</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+        <v>-15375</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>6856</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-6856</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-22231</v>
+      </c>
       <c r="AD5" t="n">
-        <v>-921602</v>
+        <v>-233794</v>
       </c>
       <c r="AE5" t="n">
-        <v>921602</v>
+        <v>233794</v>
       </c>
       <c r="AF5" t="n">
-        <v>75986</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-10753</v>
-      </c>
+        <v>81857</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>856369</v>
+        <v>151937</v>
       </c>
       <c r="AI5" t="n">
-        <v>78142</v>
+        <v>7852</v>
       </c>
       <c r="AJ5" t="n">
-        <v>778227</v>
+        <v>144085</v>
       </c>
       <c r="AK5" t="n">
-        <v>152765</v>
+        <v>42085</v>
       </c>
       <c r="AL5" t="n">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="AM5" t="n">
-        <v>607462</v>
+        <v>78000</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>717484</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-948581</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-948581</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-231097</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-231097</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-120045</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="L6" t="n">
+        <v>231097</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>77758132</v>
+      </c>
+      <c r="O6" t="n">
+        <v>77758132</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-837529</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>111052</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-959697</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>11116</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-231097</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>231097</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>80475</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>150622</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>57944</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>92678</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>68678</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>959697</v>
       </c>
     </row>
   </sheetData>
@@ -1108,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,419 +1346,469 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>67873334</v>
-      </c>
-      <c r="C2" t="n">
-        <v>67873334</v>
-      </c>
-      <c r="D2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-435553</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3046825</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1267016</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-4830946</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6610755</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6610755</v>
-      </c>
-      <c r="P2" t="n">
-        <v>503493</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>503493</v>
-      </c>
-      <c r="S2" t="n">
-        <v>503493</v>
-      </c>
-      <c r="T2" t="n">
-        <v>226</v>
-      </c>
-      <c r="U2" t="n">
-        <v>503267</v>
-      </c>
-      <c r="V2" t="n">
-        <v>503267</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3550318</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3482378</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>64200</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>3418178</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>67940</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>19089</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11873</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>11873</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>36978</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>36978</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>36978</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>67873334</v>
+        <v>66073334</v>
       </c>
       <c r="C3" t="n">
-        <v>67873334</v>
+        <v>66073334</v>
       </c>
       <c r="D3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="E3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="F3" t="n">
-        <v>-155852</v>
+        <v>111583</v>
       </c>
       <c r="G3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="H3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="I3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="J3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="K3" t="n">
-        <v>3295994</v>
+        <v>3403440</v>
       </c>
       <c r="L3" t="n">
         <v>1267016</v>
       </c>
       <c r="M3" t="n">
-        <v>-4581777</v>
+        <v>-4303331</v>
       </c>
       <c r="N3" t="n">
-        <v>6610755</v>
+        <v>6439755</v>
       </c>
       <c r="O3" t="n">
-        <v>6610755</v>
+        <v>6439755</v>
       </c>
       <c r="P3" t="n">
-        <v>395154</v>
+        <v>457872</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>395154</v>
+        <v>457872</v>
       </c>
       <c r="S3" t="n">
-        <v>395154</v>
+        <v>457872</v>
       </c>
       <c r="T3" t="n">
-        <v>639</v>
+        <v>22347</v>
       </c>
       <c r="U3" t="n">
-        <v>394515</v>
+        <v>435525</v>
       </c>
       <c r="V3" t="n">
-        <v>394515</v>
+        <v>435525</v>
       </c>
       <c r="W3" t="n">
-        <v>3691148</v>
+        <v>3861312</v>
       </c>
       <c r="X3" t="n">
-        <v>3451846</v>
+        <v>3291857</v>
       </c>
       <c r="Y3" t="n">
-        <v>64200</v>
+        <v>12000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>65060</v>
       </c>
       <c r="AA3" t="n">
-        <v>3387646</v>
+        <v>3214797</v>
       </c>
       <c r="AB3" t="n">
-        <v>239302</v>
+        <v>569455</v>
       </c>
       <c r="AC3" t="n">
-        <v>37142</v>
+        <v>38000</v>
       </c>
       <c r="AD3" t="n">
-        <v>6825</v>
+        <v>8310</v>
       </c>
       <c r="AE3" t="n">
-        <v>6825</v>
+        <v>8310</v>
       </c>
       <c r="AF3" t="n">
-        <v>195335</v>
+        <v>523145</v>
       </c>
       <c r="AG3" t="n">
-        <v>195335</v>
+        <v>523145</v>
       </c>
       <c r="AH3" t="n">
-        <v>195335</v>
-      </c>
+        <v>523145</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>66073334</v>
+        <v>67873334</v>
       </c>
       <c r="C4" t="n">
-        <v>66073334</v>
+        <v>67873334</v>
       </c>
       <c r="D4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="E4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="F4" t="n">
-        <v>111583</v>
+        <v>-155852</v>
       </c>
       <c r="G4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="H4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="I4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="J4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="K4" t="n">
-        <v>3403440</v>
+        <v>3295994</v>
       </c>
       <c r="L4" t="n">
         <v>1267016</v>
       </c>
       <c r="M4" t="n">
-        <v>-4303331</v>
+        <v>-4581777</v>
       </c>
       <c r="N4" t="n">
-        <v>6439755</v>
+        <v>6610755</v>
       </c>
       <c r="O4" t="n">
-        <v>6439755</v>
+        <v>6610755</v>
       </c>
       <c r="P4" t="n">
-        <v>457872</v>
+        <v>395154</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>457872</v>
+        <v>395154</v>
       </c>
       <c r="S4" t="n">
-        <v>457872</v>
+        <v>395154</v>
       </c>
       <c r="T4" t="n">
-        <v>22347</v>
+        <v>639</v>
       </c>
       <c r="U4" t="n">
-        <v>435525</v>
+        <v>394515</v>
       </c>
       <c r="V4" t="n">
-        <v>435525</v>
+        <v>394515</v>
       </c>
       <c r="W4" t="n">
-        <v>3861312</v>
+        <v>3691148</v>
       </c>
       <c r="X4" t="n">
-        <v>3291857</v>
+        <v>3451846</v>
       </c>
       <c r="Y4" t="n">
-        <v>12000</v>
+        <v>64200</v>
       </c>
       <c r="Z4" t="n">
-        <v>65060</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3214797</v>
+        <v>3387646</v>
       </c>
       <c r="AB4" t="n">
-        <v>569455</v>
+        <v>239302</v>
       </c>
       <c r="AC4" t="n">
-        <v>38000</v>
+        <v>37142</v>
       </c>
       <c r="AD4" t="n">
-        <v>8310</v>
+        <v>6825</v>
       </c>
       <c r="AE4" t="n">
-        <v>8310</v>
+        <v>6825</v>
       </c>
       <c r="AF4" t="n">
-        <v>523145</v>
+        <v>195335</v>
       </c>
       <c r="AG4" t="n">
-        <v>523145</v>
+        <v>195335</v>
       </c>
       <c r="AH4" t="n">
-        <v>523145</v>
-      </c>
+        <v>195335</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>64848336</v>
+        <v>67873334</v>
       </c>
       <c r="C5" t="n">
-        <v>64848336</v>
+        <v>67873334</v>
       </c>
       <c r="D5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="E5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="F5" t="n">
-        <v>2002064</v>
+        <v>-435553</v>
       </c>
       <c r="G5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="H5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="I5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="J5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="K5" t="n">
-        <v>3721272</v>
+        <v>3046825</v>
       </c>
       <c r="L5" t="n">
-        <v>1274519</v>
+        <v>1267016</v>
       </c>
       <c r="M5" t="n">
-        <v>-3802124</v>
+        <v>-4830946</v>
       </c>
       <c r="N5" t="n">
-        <v>6248877</v>
+        <v>6610755</v>
       </c>
       <c r="O5" t="n">
-        <v>6248877</v>
+        <v>6610755</v>
       </c>
       <c r="P5" t="n">
-        <v>226660</v>
+        <v>503493</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>226660</v>
+        <v>503493</v>
       </c>
       <c r="S5" t="n">
-        <v>226660</v>
+        <v>503493</v>
       </c>
       <c r="T5" t="n">
-        <v>19984</v>
+        <v>226</v>
       </c>
       <c r="U5" t="n">
-        <v>206676</v>
+        <v>503267</v>
       </c>
       <c r="V5" t="n">
-        <v>206676</v>
+        <v>503267</v>
       </c>
       <c r="W5" t="n">
-        <v>3947932</v>
+        <v>3550318</v>
       </c>
       <c r="X5" t="n">
-        <v>1719208</v>
+        <v>3482378</v>
       </c>
       <c r="Y5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>64200</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>1707208</v>
+        <v>3418178</v>
       </c>
       <c r="AB5" t="n">
-        <v>2228724</v>
+        <v>67940</v>
       </c>
       <c r="AC5" t="n">
-        <v>14987</v>
+        <v>19089</v>
       </c>
       <c r="AD5" t="n">
-        <v>19985</v>
+        <v>11873</v>
       </c>
       <c r="AE5" t="n">
-        <v>19985</v>
+        <v>11873</v>
       </c>
       <c r="AF5" t="n">
-        <v>2193752</v>
+        <v>36978</v>
       </c>
       <c r="AG5" t="n">
-        <v>2193752</v>
+        <v>36978</v>
       </c>
       <c r="AH5" t="n">
-        <v>2193752</v>
+        <v>36978</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>81294697</v>
+      </c>
+      <c r="C6" t="n">
+        <v>81294697</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-567377</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2571120</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1295962</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-5899572</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7174730</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7174730</v>
+      </c>
+      <c r="P6" t="n">
+        <v>780095</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>780095</v>
+      </c>
+      <c r="S6" t="n">
+        <v>756933</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>756933</v>
+      </c>
+      <c r="V6" t="n">
+        <v>756933</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3351215</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3138497</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>64200</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>3074297</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>212718</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>41290</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>57098</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>57098</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>114330</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>114330</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>114330</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>23162</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,343 +1991,447 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Capital Expenditure</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Capital Expenditure Reported</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Asset Impairment Charge</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-127825</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>36978</v>
-      </c>
-      <c r="H2" t="n">
-        <v>195335</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-158357</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2603050</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>-30532</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-30532</v>
-      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2603050</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2603050</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-30532</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-127825</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-127825</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>121344</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>108340</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>18052</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-5048</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>-249169</v>
-      </c>
+        <v>19559</v>
+      </c>
+      <c r="V2" t="n">
+        <v>19559</v>
+      </c>
+      <c r="W2" t="n">
+        <v>19559</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>-9459</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-10753</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>462462</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-347889</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>-1679607</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
-        <v>195335</v>
+        <v>523145</v>
       </c>
       <c r="H3" t="n">
-        <v>523145</v>
+        <v>2193752</v>
       </c>
       <c r="I3" t="n">
-        <v>-327810</v>
+        <v>-1670607</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>9000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>20079</v>
+        <v>-1322131</v>
       </c>
       <c r="T3" t="n">
-        <v>20079</v>
+        <v>-1322131</v>
       </c>
       <c r="U3" t="n">
-        <v>-52200</v>
-      </c>
-      <c r="V3" t="n">
-        <v>72279</v>
-      </c>
-      <c r="W3" t="n">
-        <v>72279</v>
-      </c>
+        <v>-1322131</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-347889</v>
+        <v>-357476</v>
       </c>
       <c r="Y3" t="n">
-        <v>-347889</v>
+        <v>-357476</v>
       </c>
       <c r="Z3" t="n">
-        <v>-69443</v>
+        <v>143731</v>
       </c>
       <c r="AA3" t="n">
-        <v>-136846</v>
+        <v>220129</v>
       </c>
       <c r="AB3" t="n">
-        <v>65918</v>
+        <v>-88073</v>
       </c>
       <c r="AC3" t="n">
-        <v>1485</v>
+        <v>11675</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-278446</v>
-      </c>
+        <v>-501207</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-1322131</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-1322131</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-357476</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+        <v>-347889</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>195335</v>
+      </c>
+      <c r="H4" t="n">
         <v>523145</v>
       </c>
-      <c r="H4" t="n">
-        <v>2193752</v>
-      </c>
       <c r="I4" t="n">
-        <v>-1670607</v>
+        <v>-327810</v>
       </c>
       <c r="J4" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-1322131</v>
+        <v>20079</v>
       </c>
       <c r="T4" t="n">
-        <v>-1322131</v>
+        <v>20079</v>
       </c>
       <c r="U4" t="n">
-        <v>-1322131</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+        <v>-52200</v>
+      </c>
+      <c r="V4" t="n">
+        <v>72279</v>
+      </c>
+      <c r="W4" t="n">
+        <v>72279</v>
+      </c>
       <c r="X4" t="n">
-        <v>-357476</v>
+        <v>-347889</v>
       </c>
       <c r="Y4" t="n">
-        <v>-357476</v>
+        <v>-347889</v>
       </c>
       <c r="Z4" t="n">
-        <v>143731</v>
+        <v>-69443</v>
       </c>
       <c r="AA4" t="n">
-        <v>220129</v>
+        <v>-136846</v>
       </c>
       <c r="AB4" t="n">
-        <v>-88073</v>
+        <v>65918</v>
       </c>
       <c r="AC4" t="n">
-        <v>11675</v>
+        <v>1485</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-501207</v>
-      </c>
+        <v>-278446</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-465817</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-40000</v>
-      </c>
+        <v>-158357</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>2603050</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>2193752</v>
+        <v>36978</v>
       </c>
       <c r="H5" t="n">
-        <v>76960</v>
+        <v>195335</v>
       </c>
       <c r="I5" t="n">
-        <v>2116792</v>
+        <v>-158357</v>
       </c>
       <c r="J5" t="n">
-        <v>2563050</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2563050</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>2603050</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2603050</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-40000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>19559</v>
+        <v>-30532</v>
       </c>
       <c r="T5" t="n">
-        <v>19559</v>
+        <v>-30532</v>
       </c>
       <c r="U5" t="n">
-        <v>19559</v>
-      </c>
-      <c r="V5" t="n">
-        <v>19559</v>
-      </c>
-      <c r="W5" t="n">
-        <v>19559</v>
-      </c>
+        <v>-30532</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-465817</v>
+        <v>-127825</v>
       </c>
       <c r="Y5" t="n">
-        <v>-465817</v>
+        <v>-127825</v>
       </c>
       <c r="Z5" t="n">
-        <v>4076</v>
+        <v>128200</v>
       </c>
       <c r="AA5" t="n">
-        <v>28522</v>
+        <v>115196</v>
       </c>
       <c r="AB5" t="n">
-        <v>-14987</v>
+        <v>18052</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9459</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-9459</v>
-      </c>
+        <v>-5048</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-10753</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>462462</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
+        <v>-6856</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-921602</v>
+        <v>-249169</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-30532</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-30532</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-649783</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>727135</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>114330</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36978</v>
+      </c>
+      <c r="I6" t="n">
+        <v>77352</v>
+      </c>
+      <c r="J6" t="n">
+        <v>727135</v>
+      </c>
+      <c r="K6" t="n">
+        <v>727135</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>727135</v>
+      </c>
+      <c r="N6" t="n">
+        <v>727135</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-486100</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-486100</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-163683</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-163683</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>56298</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>123724</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-22201</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-45225</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-111052</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>-1068626</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-486100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-486100</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>959697</v>
       </c>
     </row>
   </sheetData>
@@ -2222,7 +2445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DY2"/>
+  <dimension ref="A1:EA2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2378,182 +2601,182 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>bidSize</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bidSize</t>
+          <t>askSize</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>askSize</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
@@ -2593,280 +2816,290 @@
       </c>
       <c r="BV1" t="inlineStr">
         <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -2950,7 +3183,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Farshad  Shirvani M.Sc., MSc. Geol.', 'age': 58, 'title': 'Founder, President, CEO &amp; Director', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Anke  Woodworth B.Sc.', 'age': 47, 'title': 'CFO, Company Secretary &amp; Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 3111, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Erik Andre Ostensoe B.Sc., P. Geo', 'age': 86, 'title': 'Chief Geologist &amp; Director', 'yearBorn': 1939, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Farshad  Shirvani M.Sc., MSc. Geol.', 'age': 58, 'title': 'Founder, President, CEO &amp; Director', 'yearBorn': 1967, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Anke  Woodworth B.Sc.', 'age': 47, 'title': 'CFO, Company Secretary &amp; Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 3083, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Erik Andre Ostensoe B.Sc., P. Geo', 'age': 86, 'title': 'Chief Geologist &amp; Director', 'yearBorn': 1939, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -2968,152 +3201,150 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0.055</v>
+        <v>0.038</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.055</v>
+        <v>0.038</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.074</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Infinity</t>
-        </is>
+        <v>1.888</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6900</v>
       </c>
       <c r="AF2" t="n">
         <v>6900</v>
       </c>
       <c r="AG2" t="n">
-        <v>6900</v>
+        <v>1307</v>
       </c>
       <c r="AH2" t="n">
-        <v>2156</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.0595</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0755</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2898038</v>
       </c>
       <c r="AO2" t="n">
-        <v>4105382</v>
+        <v>4464761</v>
       </c>
       <c r="AP2" t="n">
-        <v>5563979</v>
+        <v>0.004</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.004</v>
+        <v>0.214</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.214</v>
+        <v>0.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.22</v>
+        <v>0.0005</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0005</v>
+        <v>0.06931</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.09241000000000001</v>
+        <v>0.07016749999999999</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0690175</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="AZ2" t="b">
-        <v>0</v>
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3010117</v>
       </c>
       <c r="BA2" t="n">
-        <v>3820203</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>74602752</v>
       </c>
       <c r="BC2" t="n">
-        <v>66865701</v>
+        <v>90563698</v>
       </c>
       <c r="BD2" t="n">
-        <v>81294697</v>
+        <v>0.17624001</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.17624001</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>90563698</v>
       </c>
       <c r="BG2" t="n">
-        <v>81294697</v>
+        <v>0.01973094</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.027376855</v>
+        <v>1.6218183</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.8446239</v>
+        <v>1767139200</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1735603200</v>
+        <v>1798675200</v>
       </c>
       <c r="BK2" t="n">
         <v>1767139200</v>
       </c>
       <c r="BL2" t="n">
-        <v>1759190400</v>
+        <v>-1068626</v>
       </c>
       <c r="BM2" t="n">
-        <v>-190553</v>
+        <v>-0.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-14.594</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.641791</v>
+        <v>0.4074074</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3121,7 +3352,7 @@
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>0.0505</v>
+        <v>0.032</v>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
@@ -3129,34 +3360,34 @@
         </is>
       </c>
       <c r="BT2" t="n">
-        <v>285179</v>
+        <v>114330</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>-206260</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.49</v>
+        <v>0.22</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02606</v>
+        <v>0.273</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.05738</v>
+        <v>-0.21118</v>
       </c>
       <c r="CA2" t="n">
-        <v>-424537</v>
+        <v>-0.38042998</v>
       </c>
       <c r="CB2" t="n">
-        <v>1560</v>
+        <v>-45950</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-163683</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
@@ -3164,180 +3395,186 @@
       <c r="CE2" t="n">
         <v>0</v>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG2" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>0CM.F</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CN2" t="n">
-        <v>-0.004499998</v>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>0.0505 - 0.0505</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1542956400000</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>-0.0059999973</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>0.032 - 0.032</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>2156</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.0465</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>11.625</v>
-      </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>7</v>
+      </c>
+      <c r="CX2" t="inlineStr">
         <is>
           <t>0.004 - 0.214</t>
         </is>
       </c>
-      <c r="CU2" t="n">
-        <v>-0.1635</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>-0.76401865</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>64.17910000000001</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1780430400</v>
-      </c>
       <c r="CY2" t="n">
-        <v>1780430400</v>
-      </c>
-      <c r="CZ2" t="b">
+        <v>-0.182</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.8504672599999999</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>40.74074</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1780945200</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1785351600</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>1785351600</v>
+      </c>
+      <c r="DE2" t="b">
         <v>1</v>
       </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.041909996</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.45352232</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.018517498</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.2683015</v>
-      </c>
       <c r="DF2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.03731</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.5383062</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.038167495</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.54394835</v>
+      </c>
+      <c r="DK2" t="n">
         <v>15</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DL2" t="n">
         <v>15</v>
       </c>
-      <c r="DH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1542956400000</v>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Casa Minerals Inc.</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
         <is>
           <t>CASA MINERALS INC.            R</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Casa Minerals Inc.</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DN2" t="n">
-        <v>1780380184</v>
-      </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DP2" t="n">
+        <v>1781849279</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>finmb_73526478</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DT2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DS2" t="n">
+      <c r="DU2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>dr_market</t>
         </is>
       </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-8.181815</v>
+      <c r="DW2" t="b">
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="DY2" t="inlineStr"/>
+        <v>-15.789467</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
